--- a/assets/constructions/examples/ctd_mr1.xlsx
+++ b/assets/constructions/examples/ctd_mr1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,21 +619,46 @@
           <t>cpdf</t>
         </is>
       </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5103-8x8x24x63R=1.5LH</t>
+          <t>HMR315.43D12.25DT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HANITA</t>
+          <t>FRESAL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5103-SPECIAL</t>
+          <t>HMR315.43DT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,35 +668,35 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="I2" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J2" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="M2" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="N2" t="n">
         <v>3</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>HA-8</t>
+          <t>HA-12</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -685,13 +710,29 @@
           <t>HA</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>h10</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>HM HARD METALL</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>HM HARD METALL</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>DIACUT</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -699,13 +740,13 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AA2" t="n">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="AB2" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
@@ -717,7 +758,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>SPECIAL-5544820</t>
+          <t>2020/FRESAL Фрезы Цельные Твердосплавные</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -730,12 +771,31 @@
       </c>
       <c r="AL2" t="b">
         <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>332.32</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>30551.41</v>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EC-H4M 20-40W20CFR1.0-104 IC900</t>
+          <t>ECA-B-3 12-25W12-83 IC08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -745,43 +805,43 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EC-H4M-CFR</t>
+          <t>ECA-B-3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PMKSH</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="J3" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="M3" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>HB-20</t>
+          <t>HB-12</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -799,13 +859,13 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>IC900</t>
+          <t>IC08</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
-          <t>AlTiN</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -813,13 +873,13 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AA3" t="n">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="AB3" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
@@ -840,64 +900,79 @@
         </is>
       </c>
       <c r="AK3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
         <v>1</v>
       </c>
-      <c r="AL3" t="b">
-        <v>1</v>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HMR310.30D08.06ST</t>
+          <t>759512035LT TIALN-LT1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FRESAL</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HMR310.30ST</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PMK</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="n">
         <v>8</v>
       </c>
-      <c r="G4" t="n">
-        <v>6.8</v>
-      </c>
       <c r="H4" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>HA-8</t>
+          <t>HA-12</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -911,11 +986,7 @@
           <t>HA</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>h10</t>
-        </is>
-      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
           <t>h6</t>
@@ -923,17 +994,13 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>HM HARD METALL</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>HM HARD METALL</t>
-        </is>
-      </c>
+          <t>TIAlN-LT1</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
-          <t>TiSiN</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -941,13 +1008,13 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AA4" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="AB4" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
@@ -959,7 +1026,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2020/FRESAL Фрезы Цельные Твердосплавные</t>
+          <t>2020/End Mills Widia Hanita RU</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -972,38 +1039,49 @@
       </c>
       <c r="AL4" t="b">
         <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EMB15180</t>
+          <t>HMR310.30D16.30ST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YG1</t>
+          <t>FRESAL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EMB15</t>
+          <t>HMR310.30ST</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PMS</t>
+          <t>PMK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>16.22</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>0.89</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>32</v>
@@ -1021,11 +1099,11 @@
         <v>32</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>HA-18</t>
+          <t>HA-16</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1041,7 +1119,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0/-0,03</t>
+          <t>h10</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1051,13 +1129,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Micro Grain Carbide</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr"/>
+          <t>HM HARD METALL</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>HM HARD METALL</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>TiSiN</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -1065,13 +1147,13 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA5" t="n">
         <v>92</v>
       </c>
       <c r="AB5" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
@@ -1083,7 +1165,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2017 - YG1 - General catalogue</t>
+          <t>2020/FRESAL Фрезы Цельные Твердосплавные</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1096,58 +1178,83 @@
       </c>
       <c r="AL5" t="b">
         <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>493.94</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>45409.73</v>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>PMK</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ECK-H7 12-26W12CFR0.6T83 IC900</t>
+          <t>SEME0101002</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ISCAR</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ECK-H7/9-CFR</t>
+          <t>SEME01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PMKSH</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>KH</t>
+        </is>
+      </c>
       <c r="F6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6</v>
+      </c>
       <c r="H6" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>26</v>
+        <v>2.5</v>
       </c>
       <c r="J6" t="n">
-        <v>26</v>
+        <v>2.5</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>26</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>26</v>
+        <v>2.5</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>HB-12</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1158,20 +1265,28 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+          <t>HA</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0/-0,03</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>IC900</t>
+          <t>Micro Grain Carbide</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
-          <t>AlTiN</t>
+          <t>Y-Coating</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1179,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AA6" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="AB6" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
@@ -1197,7 +1312,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2019/rotation-toos-2019-milling-tools.pdf</t>
+          <t>2017 - YG1 - YE-4G13</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1206,10 +1321,21 @@
         </is>
       </c>
       <c r="AK6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>PKH</t>
+        </is>
       </c>
     </row>
   </sheetData>
